--- a/etf_holdings/2026-10-21_common_daily_changes_min2.xlsx
+++ b/etf_holdings/2026-10-21_common_daily_changes_min2.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BV9"/>
+  <dimension ref="A1:BL8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -689,100 +689,50 @@
       </c>
       <c r="BC1" t="inlineStr">
         <is>
-          <t>00992A_異動類型</t>
+          <t>00407A_異動類型</t>
         </is>
       </c>
       <c r="BD1" t="inlineStr">
         <is>
-          <t>00992A_調整方向</t>
+          <t>00407A_調整方向</t>
         </is>
       </c>
       <c r="BE1" t="inlineStr">
         <is>
-          <t>00992A_股票名稱_昨日</t>
+          <t>00407A_股票名稱_昨日</t>
         </is>
       </c>
       <c r="BF1" t="inlineStr">
         <is>
-          <t>00992A_股票名稱_今日</t>
+          <t>00407A_股票名稱_今日</t>
         </is>
       </c>
       <c r="BG1" t="inlineStr">
         <is>
-          <t>00992A_權重_昨日</t>
+          <t>00407A_權重_昨日</t>
         </is>
       </c>
       <c r="BH1" t="inlineStr">
         <is>
-          <t>00992A_權重_今日</t>
+          <t>00407A_權重_今日</t>
         </is>
       </c>
       <c r="BI1" t="inlineStr">
         <is>
-          <t>00992A_權重變化</t>
+          <t>00407A_權重變化</t>
         </is>
       </c>
       <c r="BJ1" t="inlineStr">
         <is>
-          <t>00992A_股數_昨日</t>
+          <t>00407A_股數_昨日</t>
         </is>
       </c>
       <c r="BK1" t="inlineStr">
         <is>
-          <t>00992A_股數_今日</t>
+          <t>00407A_股數_今日</t>
         </is>
       </c>
       <c r="BL1" t="inlineStr">
-        <is>
-          <t>00992A_股數變化</t>
-        </is>
-      </c>
-      <c r="BM1" t="inlineStr">
-        <is>
-          <t>00407A_異動類型</t>
-        </is>
-      </c>
-      <c r="BN1" t="inlineStr">
-        <is>
-          <t>00407A_調整方向</t>
-        </is>
-      </c>
-      <c r="BO1" t="inlineStr">
-        <is>
-          <t>00407A_股票名稱_昨日</t>
-        </is>
-      </c>
-      <c r="BP1" t="inlineStr">
-        <is>
-          <t>00407A_股票名稱_今日</t>
-        </is>
-      </c>
-      <c r="BQ1" t="inlineStr">
-        <is>
-          <t>00407A_權重_昨日</t>
-        </is>
-      </c>
-      <c r="BR1" t="inlineStr">
-        <is>
-          <t>00407A_權重_今日</t>
-        </is>
-      </c>
-      <c r="BS1" t="inlineStr">
-        <is>
-          <t>00407A_權重變化</t>
-        </is>
-      </c>
-      <c r="BT1" t="inlineStr">
-        <is>
-          <t>00407A_股數_昨日</t>
-        </is>
-      </c>
-      <c r="BU1" t="inlineStr">
-        <is>
-          <t>00407A_股數_今日</t>
-        </is>
-      </c>
-      <c r="BV1" t="inlineStr">
         <is>
           <t>00407A_股數變化</t>
         </is>
@@ -893,58 +843,48 @@
       <c r="AZ2" t="inlineStr"/>
       <c r="BA2" t="inlineStr"/>
       <c r="BB2" t="inlineStr"/>
-      <c r="BC2" t="inlineStr"/>
-      <c r="BD2" t="inlineStr"/>
-      <c r="BE2" t="inlineStr"/>
-      <c r="BF2" t="inlineStr"/>
-      <c r="BG2" t="inlineStr"/>
-      <c r="BH2" t="inlineStr"/>
-      <c r="BI2" t="inlineStr"/>
-      <c r="BJ2" t="inlineStr"/>
-      <c r="BK2" t="inlineStr"/>
-      <c r="BL2" t="inlineStr"/>
-      <c r="BM2" t="inlineStr">
+      <c r="BC2" t="inlineStr">
         <is>
           <t>持續持有</t>
         </is>
       </c>
-      <c r="BN2" t="inlineStr">
+      <c r="BD2" t="inlineStr">
         <is>
           <t>加碼</t>
         </is>
       </c>
-      <c r="BO2" t="inlineStr">
+      <c r="BE2" t="inlineStr">
         <is>
           <t>南亞</t>
         </is>
       </c>
-      <c r="BP2" t="inlineStr">
+      <c r="BF2" t="inlineStr">
         <is>
           <t>南亞</t>
         </is>
       </c>
-      <c r="BQ2" t="inlineStr">
+      <c r="BG2" t="inlineStr">
         <is>
           <t>0.99%</t>
         </is>
       </c>
-      <c r="BR2" t="inlineStr">
+      <c r="BH2" t="inlineStr">
         <is>
           <t>2.13%</t>
         </is>
       </c>
-      <c r="BS2" t="inlineStr">
+      <c r="BI2" t="inlineStr">
         <is>
           <t>+1.14%</t>
         </is>
       </c>
-      <c r="BT2" t="n">
+      <c r="BJ2" t="n">
         <v>695000</v>
       </c>
-      <c r="BU2" t="n">
+      <c r="BK2" t="n">
         <v>1395000</v>
       </c>
-      <c r="BV2" t="inlineStr">
+      <c r="BL2" t="inlineStr">
         <is>
           <t>700,000</t>
         </is>
@@ -1055,58 +995,48 @@
       <c r="AZ3" t="inlineStr"/>
       <c r="BA3" t="inlineStr"/>
       <c r="BB3" t="inlineStr"/>
-      <c r="BC3" t="inlineStr"/>
-      <c r="BD3" t="inlineStr"/>
-      <c r="BE3" t="inlineStr"/>
-      <c r="BF3" t="inlineStr"/>
-      <c r="BG3" t="inlineStr"/>
-      <c r="BH3" t="inlineStr"/>
-      <c r="BI3" t="inlineStr"/>
-      <c r="BJ3" t="inlineStr"/>
-      <c r="BK3" t="inlineStr"/>
-      <c r="BL3" t="inlineStr"/>
-      <c r="BM3" t="inlineStr">
+      <c r="BC3" t="inlineStr">
         <is>
           <t>持續持有</t>
         </is>
       </c>
-      <c r="BN3" t="inlineStr">
+      <c r="BD3" t="inlineStr">
         <is>
           <t>減碼</t>
         </is>
       </c>
-      <c r="BO3" t="inlineStr">
+      <c r="BE3" t="inlineStr">
         <is>
           <t>智邦</t>
         </is>
       </c>
-      <c r="BP3" t="inlineStr">
+      <c r="BF3" t="inlineStr">
         <is>
           <t>智邦</t>
         </is>
       </c>
-      <c r="BQ3" t="inlineStr">
+      <c r="BG3" t="inlineStr">
         <is>
           <t>2.28%</t>
         </is>
       </c>
-      <c r="BR3" t="inlineStr">
+      <c r="BH3" t="inlineStr">
         <is>
           <t>1.56%</t>
         </is>
       </c>
-      <c r="BS3" t="inlineStr">
+      <c r="BI3" t="inlineStr">
         <is>
           <t>-0.72%</t>
         </is>
       </c>
-      <c r="BT3" t="n">
+      <c r="BJ3" t="n">
         <v>240000</v>
       </c>
-      <c r="BU3" t="n">
+      <c r="BK3" t="n">
         <v>180000</v>
       </c>
-      <c r="BV3" t="inlineStr">
+      <c r="BL3" t="inlineStr">
         <is>
           <t>-60,000</t>
         </is>
@@ -1263,16 +1193,6 @@
       <c r="BJ4" t="inlineStr"/>
       <c r="BK4" t="inlineStr"/>
       <c r="BL4" t="inlineStr"/>
-      <c r="BM4" t="inlineStr"/>
-      <c r="BN4" t="inlineStr"/>
-      <c r="BO4" t="inlineStr"/>
-      <c r="BP4" t="inlineStr"/>
-      <c r="BQ4" t="inlineStr"/>
-      <c r="BR4" t="inlineStr"/>
-      <c r="BS4" t="inlineStr"/>
-      <c r="BT4" t="inlineStr"/>
-      <c r="BU4" t="inlineStr"/>
-      <c r="BV4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1379,58 +1299,48 @@
       <c r="AZ5" t="inlineStr"/>
       <c r="BA5" t="inlineStr"/>
       <c r="BB5" t="inlineStr"/>
-      <c r="BC5" t="inlineStr"/>
-      <c r="BD5" t="inlineStr"/>
-      <c r="BE5" t="inlineStr"/>
-      <c r="BF5" t="inlineStr"/>
-      <c r="BG5" t="inlineStr"/>
-      <c r="BH5" t="inlineStr"/>
-      <c r="BI5" t="inlineStr"/>
-      <c r="BJ5" t="inlineStr"/>
-      <c r="BK5" t="inlineStr"/>
-      <c r="BL5" t="inlineStr"/>
-      <c r="BM5" t="inlineStr">
+      <c r="BC5" t="inlineStr">
         <is>
           <t>持續持有</t>
         </is>
       </c>
-      <c r="BN5" t="inlineStr">
+      <c r="BD5" t="inlineStr">
         <is>
           <t>加碼</t>
         </is>
       </c>
-      <c r="BO5" t="inlineStr">
+      <c r="BE5" t="inlineStr">
         <is>
           <t>欣興</t>
         </is>
       </c>
-      <c r="BP5" t="inlineStr">
+      <c r="BF5" t="inlineStr">
         <is>
           <t>欣興</t>
         </is>
       </c>
-      <c r="BQ5" t="inlineStr">
+      <c r="BG5" t="inlineStr">
         <is>
           <t>5.58%</t>
         </is>
       </c>
-      <c r="BR5" t="inlineStr">
+      <c r="BH5" t="inlineStr">
         <is>
           <t>6.28%</t>
         </is>
       </c>
-      <c r="BS5" t="inlineStr">
+      <c r="BI5" t="inlineStr">
         <is>
           <t>+0.70%</t>
         </is>
       </c>
-      <c r="BT5" t="n">
+      <c r="BJ5" t="n">
         <v>1097000</v>
       </c>
-      <c r="BU5" t="n">
+      <c r="BK5" t="n">
         <v>1197000</v>
       </c>
-      <c r="BV5" t="inlineStr">
+      <c r="BL5" t="inlineStr">
         <is>
           <t>100,000</t>
         </is>
@@ -1569,26 +1479,16 @@
       <c r="BJ6" t="inlineStr"/>
       <c r="BK6" t="inlineStr"/>
       <c r="BL6" t="inlineStr"/>
-      <c r="BM6" t="inlineStr"/>
-      <c r="BN6" t="inlineStr"/>
-      <c r="BO6" t="inlineStr"/>
-      <c r="BP6" t="inlineStr"/>
-      <c r="BQ6" t="inlineStr"/>
-      <c r="BR6" t="inlineStr"/>
-      <c r="BS6" t="inlineStr"/>
-      <c r="BT6" t="inlineStr"/>
-      <c r="BU6" t="inlineStr"/>
-      <c r="BV6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>3264</t>
+          <t>3711</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>欣銓</t>
+          <t>日月光投控</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -1596,75 +1496,111 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>00981A,00992A</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
+          <t>00982A,00991A</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="O7" t="inlineStr">
         <is>
           <t>持續持有</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="P7" t="inlineStr">
         <is>
           <t>加碼</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>欣銓</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>欣銓</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>0.24%</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>0.47%</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>+0.23%</t>
-        </is>
-      </c>
-      <c r="L7" t="n">
-        <v>2657000</v>
-      </c>
-      <c r="M7" t="n">
-        <v>4827000</v>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>2,170,000</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr"/>
-      <c r="P7" t="inlineStr"/>
-      <c r="Q7" t="inlineStr"/>
-      <c r="R7" t="inlineStr"/>
-      <c r="S7" t="inlineStr"/>
-      <c r="T7" t="inlineStr"/>
-      <c r="U7" t="inlineStr"/>
-      <c r="V7" t="inlineStr"/>
-      <c r="W7" t="inlineStr"/>
-      <c r="X7" t="inlineStr"/>
-      <c r="Y7" t="inlineStr"/>
-      <c r="Z7" t="inlineStr"/>
-      <c r="AA7" t="inlineStr"/>
-      <c r="AB7" t="inlineStr"/>
-      <c r="AC7" t="inlineStr"/>
-      <c r="AD7" t="inlineStr"/>
-      <c r="AE7" t="inlineStr"/>
-      <c r="AF7" t="inlineStr"/>
-      <c r="AG7" t="inlineStr"/>
-      <c r="AH7" t="inlineStr"/>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>日月光投控</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>日月光投控</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>1.82%</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>+0.07%</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>-1.75%</t>
+        </is>
+      </c>
+      <c r="V7" t="n">
+        <v>1900000</v>
+      </c>
+      <c r="W7" t="n">
+        <v>2100000</v>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>200,000</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>日月光投控</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>日月光投控</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>1.26%</t>
+        </is>
+      </c>
+      <c r="AD7" t="inlineStr">
+        <is>
+          <t>1.33%</t>
+        </is>
+      </c>
+      <c r="AE7" t="inlineStr">
+        <is>
+          <t>+0.07%</t>
+        </is>
+      </c>
+      <c r="AF7" t="n">
+        <v>883000</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>933000</v>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>50,000</t>
+        </is>
+      </c>
       <c r="AI7" t="inlineStr"/>
       <c r="AJ7" t="inlineStr"/>
       <c r="AK7" t="inlineStr"/>
@@ -1685,54 +1621,26 @@
       <c r="AZ7" t="inlineStr"/>
       <c r="BA7" t="inlineStr"/>
       <c r="BB7" t="inlineStr"/>
-      <c r="BC7" t="inlineStr">
-        <is>
-          <t>新增</t>
-        </is>
-      </c>
-      <c r="BD7" t="inlineStr">
-        <is>
-          <t>新納入</t>
-        </is>
-      </c>
+      <c r="BC7" t="inlineStr"/>
+      <c r="BD7" t="inlineStr"/>
       <c r="BE7" t="inlineStr"/>
-      <c r="BF7" t="inlineStr">
-        <is>
-          <t>欣銓</t>
-        </is>
-      </c>
+      <c r="BF7" t="inlineStr"/>
       <c r="BG7" t="inlineStr"/>
-      <c r="BH7" t="inlineStr">
-        <is>
-          <t>0.27%</t>
-        </is>
-      </c>
+      <c r="BH7" t="inlineStr"/>
       <c r="BI7" t="inlineStr"/>
       <c r="BJ7" t="inlineStr"/>
-      <c r="BK7" t="n">
-        <v>500000</v>
-      </c>
+      <c r="BK7" t="inlineStr"/>
       <c r="BL7" t="inlineStr"/>
-      <c r="BM7" t="inlineStr"/>
-      <c r="BN7" t="inlineStr"/>
-      <c r="BO7" t="inlineStr"/>
-      <c r="BP7" t="inlineStr"/>
-      <c r="BQ7" t="inlineStr"/>
-      <c r="BR7" t="inlineStr"/>
-      <c r="BS7" t="inlineStr"/>
-      <c r="BT7" t="inlineStr"/>
-      <c r="BU7" t="inlineStr"/>
-      <c r="BV7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>3711</t>
+          <t>6669</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>日月光投控</t>
+          <t>緯穎</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -1740,7 +1648,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>00982A,00991A</t>
+          <t>00407A,00985A</t>
         </is>
       </c>
       <c r="E8" t="inlineStr"/>
@@ -1753,98 +1661,26 @@
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>持續持有</t>
-        </is>
-      </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>加碼</t>
-        </is>
-      </c>
-      <c r="Q8" t="inlineStr">
-        <is>
-          <t>日月光投控</t>
-        </is>
-      </c>
-      <c r="R8" t="inlineStr">
-        <is>
-          <t>日月光投控</t>
-        </is>
-      </c>
-      <c r="S8" t="inlineStr">
-        <is>
-          <t>1.82%</t>
-        </is>
-      </c>
-      <c r="T8" t="inlineStr">
-        <is>
-          <t>+0.07%</t>
-        </is>
-      </c>
-      <c r="U8" t="inlineStr">
-        <is>
-          <t>-1.75%</t>
-        </is>
-      </c>
-      <c r="V8" t="n">
-        <v>1900000</v>
-      </c>
-      <c r="W8" t="n">
-        <v>2100000</v>
-      </c>
-      <c r="X8" t="inlineStr">
-        <is>
-          <t>200,000</t>
-        </is>
-      </c>
-      <c r="Y8" t="inlineStr">
-        <is>
-          <t>持續持有</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>加碼</t>
-        </is>
-      </c>
-      <c r="AA8" t="inlineStr">
-        <is>
-          <t>日月光投控</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>日月光投控</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>1.26%</t>
-        </is>
-      </c>
-      <c r="AD8" t="inlineStr">
-        <is>
-          <t>1.33%</t>
-        </is>
-      </c>
-      <c r="AE8" t="inlineStr">
-        <is>
-          <t>+0.07%</t>
-        </is>
-      </c>
-      <c r="AF8" t="n">
-        <v>883000</v>
-      </c>
-      <c r="AG8" t="n">
-        <v>933000</v>
-      </c>
-      <c r="AH8" t="inlineStr">
-        <is>
-          <t>50,000</t>
-        </is>
-      </c>
+      <c r="O8" t="inlineStr"/>
+      <c r="P8" t="inlineStr"/>
+      <c r="Q8" t="inlineStr"/>
+      <c r="R8" t="inlineStr"/>
+      <c r="S8" t="inlineStr"/>
+      <c r="T8" t="inlineStr"/>
+      <c r="U8" t="inlineStr"/>
+      <c r="V8" t="inlineStr"/>
+      <c r="W8" t="inlineStr"/>
+      <c r="X8" t="inlineStr"/>
+      <c r="Y8" t="inlineStr"/>
+      <c r="Z8" t="inlineStr"/>
+      <c r="AA8" t="inlineStr"/>
+      <c r="AB8" t="inlineStr"/>
+      <c r="AC8" t="inlineStr"/>
+      <c r="AD8" t="inlineStr"/>
+      <c r="AE8" t="inlineStr"/>
+      <c r="AF8" t="inlineStr"/>
+      <c r="AG8" t="inlineStr"/>
+      <c r="AH8" t="inlineStr"/>
       <c r="AI8" t="inlineStr"/>
       <c r="AJ8" t="inlineStr"/>
       <c r="AK8" t="inlineStr"/>
@@ -1855,194 +1691,94 @@
       <c r="AP8" t="inlineStr"/>
       <c r="AQ8" t="inlineStr"/>
       <c r="AR8" t="inlineStr"/>
-      <c r="AS8" t="inlineStr"/>
-      <c r="AT8" t="inlineStr"/>
-      <c r="AU8" t="inlineStr"/>
-      <c r="AV8" t="inlineStr"/>
-      <c r="AW8" t="inlineStr"/>
-      <c r="AX8" t="inlineStr"/>
-      <c r="AY8" t="inlineStr"/>
-      <c r="AZ8" t="inlineStr"/>
-      <c r="BA8" t="inlineStr"/>
-      <c r="BB8" t="inlineStr"/>
-      <c r="BC8" t="inlineStr"/>
-      <c r="BD8" t="inlineStr"/>
-      <c r="BE8" t="inlineStr"/>
-      <c r="BF8" t="inlineStr"/>
-      <c r="BG8" t="inlineStr"/>
-      <c r="BH8" t="inlineStr"/>
-      <c r="BI8" t="inlineStr"/>
-      <c r="BJ8" t="inlineStr"/>
-      <c r="BK8" t="inlineStr"/>
-      <c r="BL8" t="inlineStr"/>
-      <c r="BM8" t="inlineStr"/>
-      <c r="BN8" t="inlineStr"/>
-      <c r="BO8" t="inlineStr"/>
-      <c r="BP8" t="inlineStr"/>
-      <c r="BQ8" t="inlineStr"/>
-      <c r="BR8" t="inlineStr"/>
-      <c r="BS8" t="inlineStr"/>
-      <c r="BT8" t="inlineStr"/>
-      <c r="BU8" t="inlineStr"/>
-      <c r="BV8" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>6669</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
+      <c r="AS8" t="inlineStr">
+        <is>
+          <t>持續持有</t>
+        </is>
+      </c>
+      <c r="AT8" t="inlineStr">
+        <is>
+          <t>加碼</t>
+        </is>
+      </c>
+      <c r="AU8" t="inlineStr">
         <is>
           <t>緯穎</t>
         </is>
       </c>
-      <c r="C9" t="n">
-        <v>2</v>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>00407A,00985A</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
-      <c r="O9" t="inlineStr"/>
-      <c r="P9" t="inlineStr"/>
-      <c r="Q9" t="inlineStr"/>
-      <c r="R9" t="inlineStr"/>
-      <c r="S9" t="inlineStr"/>
-      <c r="T9" t="inlineStr"/>
-      <c r="U9" t="inlineStr"/>
-      <c r="V9" t="inlineStr"/>
-      <c r="W9" t="inlineStr"/>
-      <c r="X9" t="inlineStr"/>
-      <c r="Y9" t="inlineStr"/>
-      <c r="Z9" t="inlineStr"/>
-      <c r="AA9" t="inlineStr"/>
-      <c r="AB9" t="inlineStr"/>
-      <c r="AC9" t="inlineStr"/>
-      <c r="AD9" t="inlineStr"/>
-      <c r="AE9" t="inlineStr"/>
-      <c r="AF9" t="inlineStr"/>
-      <c r="AG9" t="inlineStr"/>
-      <c r="AH9" t="inlineStr"/>
-      <c r="AI9" t="inlineStr"/>
-      <c r="AJ9" t="inlineStr"/>
-      <c r="AK9" t="inlineStr"/>
-      <c r="AL9" t="inlineStr"/>
-      <c r="AM9" t="inlineStr"/>
-      <c r="AN9" t="inlineStr"/>
-      <c r="AO9" t="inlineStr"/>
-      <c r="AP9" t="inlineStr"/>
-      <c r="AQ9" t="inlineStr"/>
-      <c r="AR9" t="inlineStr"/>
-      <c r="AS9" t="inlineStr">
+      <c r="AV8" t="inlineStr">
+        <is>
+          <t>緯穎</t>
+        </is>
+      </c>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>2.50%</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>3.54%</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>+1.04%</t>
+        </is>
+      </c>
+      <c r="AZ8" t="n">
+        <v>392036</v>
+      </c>
+      <c r="BA8" t="n">
+        <v>537036</v>
+      </c>
+      <c r="BB8" t="inlineStr">
+        <is>
+          <t>145,000</t>
+        </is>
+      </c>
+      <c r="BC8" t="inlineStr">
         <is>
           <t>持續持有</t>
         </is>
       </c>
-      <c r="AT9" t="inlineStr">
-        <is>
-          <t>加碼</t>
-        </is>
-      </c>
-      <c r="AU9" t="inlineStr">
+      <c r="BD8" t="inlineStr">
+        <is>
+          <t>減碼</t>
+        </is>
+      </c>
+      <c r="BE8" t="inlineStr">
         <is>
           <t>緯穎</t>
         </is>
       </c>
-      <c r="AV9" t="inlineStr">
+      <c r="BF8" t="inlineStr">
         <is>
           <t>緯穎</t>
         </is>
       </c>
-      <c r="AW9" t="inlineStr">
-        <is>
-          <t>2.50%</t>
-        </is>
-      </c>
-      <c r="AX9" t="inlineStr">
-        <is>
-          <t>3.54%</t>
-        </is>
-      </c>
-      <c r="AY9" t="inlineStr">
-        <is>
-          <t>+1.04%</t>
-        </is>
-      </c>
-      <c r="AZ9" t="n">
-        <v>392036</v>
-      </c>
-      <c r="BA9" t="n">
-        <v>537036</v>
-      </c>
-      <c r="BB9" t="inlineStr">
-        <is>
-          <t>145,000</t>
-        </is>
-      </c>
-      <c r="BC9" t="inlineStr"/>
-      <c r="BD9" t="inlineStr"/>
-      <c r="BE9" t="inlineStr"/>
-      <c r="BF9" t="inlineStr"/>
-      <c r="BG9" t="inlineStr"/>
-      <c r="BH9" t="inlineStr"/>
-      <c r="BI9" t="inlineStr"/>
-      <c r="BJ9" t="inlineStr"/>
-      <c r="BK9" t="inlineStr"/>
-      <c r="BL9" t="inlineStr"/>
-      <c r="BM9" t="inlineStr">
-        <is>
-          <t>持續持有</t>
-        </is>
-      </c>
-      <c r="BN9" t="inlineStr">
-        <is>
-          <t>減碼</t>
-        </is>
-      </c>
-      <c r="BO9" t="inlineStr">
-        <is>
-          <t>緯穎</t>
-        </is>
-      </c>
-      <c r="BP9" t="inlineStr">
-        <is>
-          <t>緯穎</t>
-        </is>
-      </c>
-      <c r="BQ9" t="inlineStr">
+      <c r="BG8" t="inlineStr">
         <is>
           <t>3.60%</t>
         </is>
       </c>
-      <c r="BR9" t="inlineStr">
+      <c r="BH8" t="inlineStr">
         <is>
           <t>2.40%</t>
         </is>
       </c>
-      <c r="BS9" t="inlineStr">
+      <c r="BI8" t="inlineStr">
         <is>
           <t>-1.20%</t>
         </is>
       </c>
-      <c r="BT9" t="n">
+      <c r="BJ8" t="n">
         <v>387644</v>
       </c>
-      <c r="BU9" t="n">
+      <c r="BK8" t="n">
         <v>267644</v>
       </c>
-      <c r="BV9" t="inlineStr">
+      <c r="BL8" t="inlineStr">
         <is>
           <t>-120,000</t>
         </is>
